--- a/data/derived_data/2_RarefyData/Dataset_1/ps_ITS_filt20_Dataset_1_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_ITS_filt20_Dataset_1_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="451">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -182,6 +182,9 @@
     <t xml:space="preserve">Cluster_107</t>
   </si>
   <si>
+    <t xml:space="preserve">pulcherrima</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_108</t>
   </si>
   <si>
@@ -569,6 +572,24 @@
     <t xml:space="preserve">Cluster_240</t>
   </si>
   <si>
+    <t xml:space="preserve">Viridiplantae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streptophyta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnoliopsida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_242</t>
   </si>
   <si>
@@ -806,12 +827,21 @@
     <t xml:space="preserve">Cluster_368</t>
   </si>
   <si>
+    <t xml:space="preserve">Martiniozyma</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_37</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_371</t>
   </si>
   <si>
+    <t xml:space="preserve">Prunus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avium</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_375</t>
   </si>
   <si>
@@ -983,6 +1013,9 @@
     <t xml:space="preserve">Cluster_576</t>
   </si>
   <si>
+    <t xml:space="preserve">sulcatus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_58</t>
   </si>
   <si>
@@ -1103,9 +1136,6 @@
     <t xml:space="preserve">Starmerella magnoliae</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_729</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
@@ -1127,6 +1157,9 @@
     <t xml:space="preserve">Cluster_744</t>
   </si>
   <si>
+    <t xml:space="preserve">avinus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_751</t>
   </si>
   <si>
@@ -1139,9 +1172,33 @@
     <t xml:space="preserve">Cluster_77</t>
   </si>
   <si>
+    <t xml:space="preserve">Chromista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oomycota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peronosporomycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peronosporales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peronosporaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phytophthora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cactorum</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_777</t>
   </si>
   <si>
+    <t xml:space="preserve">chrysoperlae</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_778</t>
   </si>
   <si>
@@ -1254,6 +1311,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pimensis</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_9</t>
@@ -1846,22 +1906,22 @@
         <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
         <v>20</v>
@@ -1950,30 +2010,30 @@
         <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -1999,7 +2059,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -2025,7 +2085,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -2034,24 +2094,24 @@
         <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -2077,7 +2137,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -2098,12 +2158,12 @@
         <v>24</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
@@ -2129,33 +2189,33 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -2176,12 +2236,12 @@
         <v>24</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
@@ -2202,12 +2262,12 @@
         <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -2216,24 +2276,24 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -2254,12 +2314,12 @@
         <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -2268,24 +2328,24 @@
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -2294,16 +2354,16 @@
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
         <v>20</v>
@@ -2311,7 +2371,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -2337,7 +2397,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
@@ -2349,13 +2409,13 @@
         <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s">
         <v>20</v>
@@ -2363,7 +2423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -2372,10 +2432,10 @@
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -2389,7 +2449,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -2410,12 +2470,12 @@
         <v>24</v>
       </c>
       <c r="H30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -2427,21 +2487,21 @@
         <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -2450,24 +2510,24 @@
         <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -2476,24 +2536,24 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -2505,13 +2565,13 @@
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H34" t="s">
         <v>20</v>
@@ -2519,7 +2579,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -2537,15 +2597,15 @@
         <v>19</v>
       </c>
       <c r="G35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -2566,12 +2626,12 @@
         <v>24</v>
       </c>
       <c r="H36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -2592,12 +2652,12 @@
         <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -2606,10 +2666,10 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F38" t="s">
         <v>20</v>
@@ -2623,7 +2683,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -2635,21 +2695,21 @@
         <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F39" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -2661,21 +2721,21 @@
         <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H40" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -2701,7 +2761,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -2713,10 +2773,10 @@
         <v>27</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G42" t="s">
         <v>20</v>
@@ -2727,7 +2787,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -2736,24 +2796,24 @@
         <v>33</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -2779,7 +2839,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -2794,18 +2854,18 @@
         <v>42</v>
       </c>
       <c r="F45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -2817,21 +2877,21 @@
         <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -2843,10 +2903,10 @@
         <v>27</v>
       </c>
       <c r="E47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G47" t="s">
         <v>20</v>
@@ -2857,7 +2917,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -2866,24 +2926,24 @@
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -2892,16 +2952,16 @@
         <v>33</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G49" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H49" t="s">
         <v>20</v>
@@ -2909,7 +2969,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -2918,10 +2978,10 @@
         <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F50" t="s">
         <v>20</v>
@@ -2935,7 +2995,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -2950,10 +3010,10 @@
         <v>42</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H51" t="s">
         <v>20</v>
@@ -2961,7 +3021,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
@@ -2970,7 +3030,7 @@
         <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
@@ -2987,7 +3047,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
@@ -3013,7 +3073,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
@@ -3022,24 +3082,24 @@
         <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s">
         <v>9</v>
@@ -3048,24 +3108,24 @@
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G55" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -3074,16 +3134,16 @@
         <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H56" t="s">
         <v>20</v>
@@ -3091,7 +3151,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
@@ -3100,24 +3160,24 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
@@ -3132,18 +3192,18 @@
         <v>42</v>
       </c>
       <c r="F58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H58" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
@@ -3152,24 +3212,24 @@
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F59" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G59" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
@@ -3178,10 +3238,10 @@
         <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F60" t="s">
         <v>20</v>
@@ -3195,7 +3255,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
@@ -3221,7 +3281,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
@@ -3242,12 +3302,12 @@
         <v>24</v>
       </c>
       <c r="H62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -3256,16 +3316,16 @@
         <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H63" t="s">
         <v>20</v>
@@ -3273,7 +3333,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B64" t="s">
         <v>9</v>
@@ -3299,25 +3359,25 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B65" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F65" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G65" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H65" t="s">
         <v>20</v>
@@ -3325,7 +3385,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -3334,24 +3394,24 @@
         <v>33</v>
       </c>
       <c r="D66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B67" t="s">
         <v>9</v>
@@ -3360,10 +3420,10 @@
         <v>33</v>
       </c>
       <c r="D67" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E67" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F67" t="s">
         <v>20</v>
@@ -3377,25 +3437,25 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G68" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H68" t="s">
         <v>20</v>
@@ -3403,7 +3463,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B69" t="s">
         <v>9</v>
@@ -3415,13 +3475,13 @@
         <v>27</v>
       </c>
       <c r="E69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F69" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G69" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H69" t="s">
         <v>20</v>
@@ -3429,7 +3489,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -3438,7 +3498,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
@@ -3455,7 +3515,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -3464,42 +3524,42 @@
         <v>33</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="D72" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="F72" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="G72" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="H72" t="s">
         <v>20</v>
@@ -3507,7 +3567,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
@@ -3533,7 +3593,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
@@ -3545,21 +3605,21 @@
         <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F74" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G74" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H74" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
@@ -3585,7 +3645,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B76" t="s">
         <v>9</v>
@@ -3594,24 +3654,24 @@
         <v>33</v>
       </c>
       <c r="D76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E76" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F76" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G76" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
@@ -3637,7 +3697,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B78" t="s">
         <v>9</v>
@@ -3646,16 +3706,16 @@
         <v>33</v>
       </c>
       <c r="D78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F78" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G78" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H78" t="s">
         <v>20</v>
@@ -3663,7 +3723,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
@@ -3675,13 +3735,13 @@
         <v>27</v>
       </c>
       <c r="E79" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F79" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G79" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H79" t="s">
         <v>20</v>
@@ -3689,7 +3749,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
@@ -3698,16 +3758,16 @@
         <v>33</v>
       </c>
       <c r="D80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F80" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s">
         <v>20</v>
@@ -3715,7 +3775,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B81" t="s">
         <v>9</v>
@@ -3727,13 +3787,13 @@
         <v>27</v>
       </c>
       <c r="E81" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G81" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H81" t="s">
         <v>20</v>
@@ -3741,7 +3801,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
@@ -3750,24 +3810,24 @@
         <v>33</v>
       </c>
       <c r="D82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E82" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F82" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G82" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H82" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B83" t="s">
         <v>9</v>
@@ -3793,7 +3853,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B84" t="s">
         <v>9</v>
@@ -3819,7 +3879,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B85" t="s">
         <v>9</v>
@@ -3845,7 +3905,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B86" t="s">
         <v>9</v>
@@ -3866,12 +3926,12 @@
         <v>24</v>
       </c>
       <c r="H86" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B87" t="s">
         <v>9</v>
@@ -3880,24 +3940,24 @@
         <v>33</v>
       </c>
       <c r="D87" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E87" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F87" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G87" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H87" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B88" t="s">
         <v>9</v>
@@ -3906,13 +3966,13 @@
         <v>33</v>
       </c>
       <c r="D88" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E88" t="s">
         <v>20</v>
       </c>
       <c r="F88" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G88" t="s">
         <v>20</v>
@@ -3923,7 +3983,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
@@ -3932,24 +3992,24 @@
         <v>33</v>
       </c>
       <c r="D89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E89" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F89" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G89" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H89" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
@@ -3975,7 +4035,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B91" t="s">
         <v>9</v>
@@ -3987,21 +4047,21 @@
         <v>27</v>
       </c>
       <c r="E91" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G91" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H91" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B92" t="s">
         <v>9</v>
@@ -4010,16 +4070,16 @@
         <v>33</v>
       </c>
       <c r="D92" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E92" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F92" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G92" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H92" t="s">
         <v>20</v>
@@ -4027,7 +4087,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
@@ -4039,21 +4099,21 @@
         <v>41</v>
       </c>
       <c r="E93" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F93" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="G93" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H93" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B94" t="s">
         <v>9</v>
@@ -4074,12 +4134,12 @@
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B95" t="s">
         <v>9</v>
@@ -4088,24 +4148,24 @@
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E95" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F95" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G95" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H95" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B96" t="s">
         <v>9</v>
@@ -4114,24 +4174,24 @@
         <v>33</v>
       </c>
       <c r="D96" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E96" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F96" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G96" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H96" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B97" t="s">
         <v>9</v>
@@ -4143,21 +4203,21 @@
         <v>27</v>
       </c>
       <c r="E97" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F97" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G97" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H97" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B98" t="s">
         <v>9</v>
@@ -4166,24 +4226,24 @@
         <v>33</v>
       </c>
       <c r="D98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E98" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F98" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G98" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H98" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B99" t="s">
         <v>9</v>
@@ -4204,30 +4264,30 @@
         <v>24</v>
       </c>
       <c r="H99" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="D100" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="E100" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="G100" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="H100" t="s">
         <v>20</v>
@@ -4235,7 +4295,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B101" t="s">
         <v>9</v>
@@ -4244,24 +4304,24 @@
         <v>33</v>
       </c>
       <c r="D101" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E101" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F101" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G101" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H101" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B102" t="s">
         <v>9</v>
@@ -4282,12 +4342,12 @@
         <v>24</v>
       </c>
       <c r="H102" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B103" t="s">
         <v>9</v>
@@ -4308,12 +4368,12 @@
         <v>24</v>
       </c>
       <c r="H103" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B104" t="s">
         <v>9</v>
@@ -4322,24 +4382,24 @@
         <v>33</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E104" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F104" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G104" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H104" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B105" t="s">
         <v>9</v>
@@ -4365,25 +4425,25 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B106" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G106" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H106" t="s">
         <v>20</v>
@@ -4391,7 +4451,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B107" t="s">
         <v>9</v>
@@ -4412,12 +4472,12 @@
         <v>53</v>
       </c>
       <c r="H107" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B108" t="s">
         <v>9</v>
@@ -4426,24 +4486,24 @@
         <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E108" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F108" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="G108" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="H108" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B109" t="s">
         <v>9</v>
@@ -4464,12 +4524,12 @@
         <v>24</v>
       </c>
       <c r="H109" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B110" t="s">
         <v>9</v>
@@ -4478,16 +4538,16 @@
         <v>33</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E110" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="G110" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H110" t="s">
         <v>20</v>
@@ -4495,7 +4555,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B111" t="s">
         <v>9</v>
@@ -4504,16 +4564,16 @@
         <v>33</v>
       </c>
       <c r="D111" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E111" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F111" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="G111" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="H111" t="s">
         <v>20</v>
@@ -4521,25 +4581,25 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B112" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D112" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G112" t="s">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="H112" t="s">
         <v>20</v>
@@ -4547,7 +4607,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B113" t="s">
         <v>9</v>
@@ -4568,64 +4628,64 @@
         <v>24</v>
       </c>
       <c r="H113" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B114" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="D114" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="E114" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="F114" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="G114" t="s">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="H114" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B115" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D115" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E115" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G115" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H115" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B116" t="s">
         <v>9</v>
@@ -4651,7 +4711,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B117" t="s">
         <v>9</v>
@@ -4672,12 +4732,12 @@
         <v>24</v>
       </c>
       <c r="H117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B118" t="s">
         <v>9</v>
@@ -4698,12 +4758,12 @@
         <v>53</v>
       </c>
       <c r="H118" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B119" t="s">
         <v>9</v>
@@ -4729,7 +4789,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B120" t="s">
         <v>9</v>
@@ -4755,33 +4815,33 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D121" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G121" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H121" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B122" t="s">
         <v>9</v>
@@ -4790,13 +4850,13 @@
         <v>10</v>
       </c>
       <c r="D122" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E122" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F122" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="G122" t="s">
         <v>20</v>
@@ -4807,7 +4867,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B123" t="s">
         <v>9</v>
@@ -4816,16 +4876,16 @@
         <v>10</v>
       </c>
       <c r="D123" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E123" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F123" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="G123" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="H123" t="s">
         <v>20</v>
@@ -4833,7 +4893,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B124" t="s">
         <v>9</v>
@@ -4842,16 +4902,16 @@
         <v>33</v>
       </c>
       <c r="D124" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E124" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F124" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G124" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H124" t="s">
         <v>20</v>
@@ -4859,59 +4919,59 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B125" t="s">
         <v>9</v>
       </c>
       <c r="C125" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D125" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E125" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F125" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G125" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H125" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B126" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C126" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D126" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E126" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F126" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G126" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H126" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B127" t="s">
         <v>9</v>
@@ -4937,7 +4997,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B128" t="s">
         <v>9</v>
@@ -4946,24 +5006,24 @@
         <v>10</v>
       </c>
       <c r="D128" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E128" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="F128" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G128" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="H128" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B129" t="s">
         <v>9</v>
@@ -4989,7 +5049,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B130" t="s">
         <v>9</v>
@@ -5015,7 +5075,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B131" t="s">
         <v>9</v>
@@ -5041,7 +5101,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B132" t="s">
         <v>9</v>
@@ -5067,7 +5127,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B133" t="s">
         <v>9</v>
@@ -5093,25 +5153,25 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B134" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D134" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E134" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F134" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G134" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H134" t="s">
         <v>20</v>
@@ -5119,7 +5179,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B135" t="s">
         <v>9</v>
@@ -5140,12 +5200,12 @@
         <v>24</v>
       </c>
       <c r="H135" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B136" t="s">
         <v>9</v>
@@ -5171,7 +5231,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B137" t="s">
         <v>9</v>
@@ -5197,25 +5257,25 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B138" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D138" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F138" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G138" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H138" t="s">
         <v>20</v>
@@ -5223,7 +5283,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B139" t="s">
         <v>9</v>
@@ -5244,12 +5304,12 @@
         <v>24</v>
       </c>
       <c r="H139" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B140" t="s">
         <v>9</v>
@@ -5258,24 +5318,24 @@
         <v>33</v>
       </c>
       <c r="D140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E140" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F140" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G140" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H140" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B141" t="s">
         <v>9</v>
@@ -5287,13 +5347,13 @@
         <v>27</v>
       </c>
       <c r="E141" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F141" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G141" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H141" t="s">
         <v>20</v>
@@ -5301,7 +5361,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B142" t="s">
         <v>9</v>
@@ -5322,12 +5382,12 @@
         <v>24</v>
       </c>
       <c r="H142" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B143" t="s">
         <v>9</v>
@@ -5353,7 +5413,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B144" t="s">
         <v>9</v>
@@ -5379,7 +5439,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B145" t="s">
         <v>9</v>
@@ -5400,12 +5460,12 @@
         <v>24</v>
       </c>
       <c r="H145" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B146" t="s">
         <v>9</v>
@@ -5420,18 +5480,18 @@
         <v>51</v>
       </c>
       <c r="F146" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="G146" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="H146" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B147" t="s">
         <v>9</v>
@@ -5457,7 +5517,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B148" t="s">
         <v>9</v>
@@ -5483,7 +5543,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B149" t="s">
         <v>9</v>
@@ -5509,7 +5569,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B150" t="s">
         <v>9</v>
@@ -5530,12 +5590,12 @@
         <v>24</v>
       </c>
       <c r="H150" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B151" t="s">
         <v>9</v>
@@ -5561,7 +5621,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B152" t="s">
         <v>9</v>
@@ -5587,7 +5647,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B153" t="s">
         <v>9</v>
@@ -5613,51 +5673,51 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B154" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="D154" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="E154" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="F154" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="G154" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="H154" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B155" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D155" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E155" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F155" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G155" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H155" t="s">
         <v>20</v>
@@ -5665,7 +5725,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B156" t="s">
         <v>9</v>
@@ -5691,7 +5751,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B157" t="s">
         <v>9</v>
@@ -5700,24 +5760,24 @@
         <v>10</v>
       </c>
       <c r="D157" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E157" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F157" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="G157" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="H157" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B158" t="s">
         <v>9</v>
@@ -5738,12 +5798,12 @@
         <v>24</v>
       </c>
       <c r="H158" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B159" t="s">
         <v>9</v>
@@ -5752,13 +5812,13 @@
         <v>10</v>
       </c>
       <c r="D159" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E159" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F159" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="G159" t="s">
         <v>20</v>
@@ -5769,7 +5829,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B160" t="s">
         <v>9</v>
@@ -5787,7 +5847,7 @@
         <v>52</v>
       </c>
       <c r="G160" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="H160" t="s">
         <v>20</v>
@@ -5795,7 +5855,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B161" t="s">
         <v>20</v>
@@ -5821,7 +5881,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B162" t="s">
         <v>20</v>
@@ -5847,7 +5907,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B163" t="s">
         <v>9</v>
@@ -5873,7 +5933,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B164" t="s">
         <v>9</v>
@@ -5882,16 +5942,16 @@
         <v>10</v>
       </c>
       <c r="D164" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E164" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F164" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="G164" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="H164" t="s">
         <v>20</v>
@@ -5899,7 +5959,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B165" t="s">
         <v>9</v>
@@ -5908,7 +5968,7 @@
         <v>33</v>
       </c>
       <c r="D165" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E165" t="s">
         <v>20</v>
@@ -5925,7 +5985,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B166" t="s">
         <v>9</v>
@@ -5934,10 +5994,10 @@
         <v>10</v>
       </c>
       <c r="D166" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E166" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F166" t="s">
         <v>20</v>
@@ -5951,25 +6011,25 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B167" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D167" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E167" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F167" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G167" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H167" t="s">
         <v>20</v>
@@ -5977,7 +6037,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B168" t="s">
         <v>9</v>
@@ -6003,7 +6063,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B169" t="s">
         <v>9</v>
@@ -6024,12 +6084,12 @@
         <v>24</v>
       </c>
       <c r="H169" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B170" t="s">
         <v>9</v>
@@ -6050,12 +6110,12 @@
         <v>24</v>
       </c>
       <c r="H170" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B171" t="s">
         <v>9</v>
@@ -6081,7 +6141,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B172" t="s">
         <v>9</v>
@@ -6102,56 +6162,56 @@
         <v>24</v>
       </c>
       <c r="H172" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B173" t="s">
         <v>9</v>
       </c>
       <c r="C173" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D173" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E173" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F173" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G173" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H173" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B174" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C174" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D174" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F174" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G174" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H174" t="s">
         <v>20</v>
@@ -6159,7 +6219,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B175" t="s">
         <v>9</v>
@@ -6168,16 +6228,16 @@
         <v>33</v>
       </c>
       <c r="D175" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E175" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F175" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G175" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H175" t="s">
         <v>20</v>
@@ -6185,7 +6245,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B176" t="s">
         <v>9</v>
@@ -6194,24 +6254,24 @@
         <v>10</v>
       </c>
       <c r="D176" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E176" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="F176" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="G176" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H176" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B177" t="s">
         <v>9</v>
@@ -6226,10 +6286,10 @@
         <v>42</v>
       </c>
       <c r="F177" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G177" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H177" t="s">
         <v>20</v>
@@ -6237,7 +6297,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B178" t="s">
         <v>9</v>
@@ -6246,24 +6306,24 @@
         <v>10</v>
       </c>
       <c r="D178" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E178" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F178" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G178" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H178" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B179" t="s">
         <v>9</v>
@@ -6278,36 +6338,36 @@
         <v>42</v>
       </c>
       <c r="F179" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G179" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H179" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B180" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C180" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D180" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F180" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G180" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H180" t="s">
         <v>20</v>
@@ -6315,7 +6375,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B181" t="s">
         <v>9</v>
@@ -6330,18 +6390,18 @@
         <v>42</v>
       </c>
       <c r="F181" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G181" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H181" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B182" t="s">
         <v>9</v>
@@ -6353,21 +6413,21 @@
         <v>11</v>
       </c>
       <c r="E182" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F182" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G182" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H182" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B183" t="s">
         <v>9</v>
@@ -6376,198 +6436,198 @@
         <v>10</v>
       </c>
       <c r="D183" t="s">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="E183" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
       <c r="F183" t="s">
-        <v>23</v>
+        <v>377</v>
       </c>
       <c r="G183" t="s">
-        <v>24</v>
+        <v>378</v>
       </c>
       <c r="H183" t="s">
-        <v>66</v>
+        <v>379</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B184" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="C184" t="s">
-        <v>10</v>
+        <v>187</v>
       </c>
       <c r="D184" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="E184" t="s">
-        <v>366</v>
+        <v>189</v>
       </c>
       <c r="F184" t="s">
-        <v>367</v>
+        <v>190</v>
       </c>
       <c r="G184" t="s">
-        <v>368</v>
+        <v>274</v>
       </c>
       <c r="H184" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D185" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E185" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F185" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G185" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H185" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B186" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C186" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E186" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F186" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G186" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B187" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C187" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D187" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E187" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F187" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G187" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H187" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B188" t="s">
-        <v>9</v>
+        <v>386</v>
       </c>
       <c r="C188" t="s">
-        <v>10</v>
+        <v>387</v>
       </c>
       <c r="D188" t="s">
-        <v>11</v>
+        <v>388</v>
       </c>
       <c r="E188" t="s">
-        <v>22</v>
+        <v>389</v>
       </c>
       <c r="F188" t="s">
-        <v>23</v>
+        <v>390</v>
       </c>
       <c r="G188" t="s">
-        <v>24</v>
+        <v>391</v>
       </c>
       <c r="H188" t="s">
-        <v>66</v>
+        <v>392</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="B189" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C189" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D189" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E189" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F189" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G189" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H189" t="s">
-        <v>20</v>
+        <v>394</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="B190" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C190" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D190" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E190" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F190" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G190" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H190" t="s">
         <v>20</v>
@@ -6575,7 +6635,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B191" t="s">
         <v>9</v>
@@ -6584,76 +6644,76 @@
         <v>10</v>
       </c>
       <c r="D191" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E191" t="s">
-        <v>28</v>
+        <v>229</v>
       </c>
       <c r="F191" t="s">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="G191" t="s">
-        <v>30</v>
+        <v>231</v>
       </c>
       <c r="H191" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="B192" t="s">
         <v>9</v>
       </c>
       <c r="C192" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D192" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E192" t="s">
-        <v>222</v>
+        <v>86</v>
       </c>
       <c r="F192" t="s">
-        <v>223</v>
+        <v>398</v>
       </c>
       <c r="G192" t="s">
-        <v>224</v>
+        <v>399</v>
       </c>
       <c r="H192" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="B193" t="s">
         <v>9</v>
       </c>
       <c r="C193" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D193" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E193" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="F193" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="G193" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="H193" t="s">
-        <v>20</v>
+        <v>403</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="B194" t="s">
         <v>9</v>
@@ -6662,33 +6722,33 @@
         <v>10</v>
       </c>
       <c r="D194" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F194" t="s">
-        <v>382</v>
+        <v>23</v>
       </c>
       <c r="G194" t="s">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="H194" t="s">
-        <v>384</v>
+        <v>56</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="B195" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C195" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D195" t="s">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="E195" t="s">
         <v>20</v>
@@ -6705,59 +6765,59 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="B196" t="s">
         <v>9</v>
       </c>
       <c r="C196" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D196" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E196" t="s">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="F196" t="s">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="G196" t="s">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="H196" t="s">
-        <v>20</v>
+        <v>410</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="B197" t="s">
         <v>9</v>
       </c>
       <c r="C197" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D197" t="s">
-        <v>177</v>
+        <v>11</v>
       </c>
       <c r="E197" t="s">
-        <v>388</v>
+        <v>22</v>
       </c>
       <c r="F197" t="s">
-        <v>389</v>
+        <v>23</v>
       </c>
       <c r="G197" t="s">
-        <v>390</v>
+        <v>24</v>
       </c>
       <c r="H197" t="s">
-        <v>391</v>
+        <v>71</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="B198" t="s">
         <v>9</v>
@@ -6778,38 +6838,38 @@
         <v>24</v>
       </c>
       <c r="H198" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="B199" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C199" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D199" t="s">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="E199" t="s">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="F199" t="s">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="G199" t="s">
-        <v>20</v>
+        <v>414</v>
       </c>
       <c r="H199" t="s">
-        <v>20</v>
+        <v>415</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="B200" t="s">
         <v>9</v>
@@ -6818,24 +6878,24 @@
         <v>10</v>
       </c>
       <c r="D200" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="E200" t="s">
-        <v>251</v>
+        <v>20</v>
       </c>
       <c r="F200" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="G200" t="s">
-        <v>395</v>
+        <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>396</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B201" t="s">
         <v>9</v>
@@ -6844,24 +6904,24 @@
         <v>10</v>
       </c>
       <c r="D201" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E201" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F201" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G201" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H201" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="B202" t="s">
         <v>9</v>
@@ -6882,12 +6942,12 @@
         <v>24</v>
       </c>
       <c r="H202" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B203" t="s">
         <v>9</v>
@@ -6908,15 +6968,15 @@
         <v>24</v>
       </c>
       <c r="H203" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="B204" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C204" t="s">
         <v>20</v>
@@ -6939,19 +6999,19 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="B205" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C205" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D205" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E205" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F205" t="s">
         <v>20</v>
@@ -6965,137 +7025,137 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="B206" t="s">
         <v>9</v>
       </c>
       <c r="C206" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D206" t="s">
-        <v>41</v>
+        <v>423</v>
       </c>
       <c r="E206" t="s">
-        <v>42</v>
+        <v>424</v>
       </c>
       <c r="F206" t="s">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="G206" t="s">
-        <v>20</v>
+        <v>426</v>
       </c>
       <c r="H206" t="s">
-        <v>20</v>
+        <v>427</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="B207" t="s">
         <v>9</v>
       </c>
       <c r="C207" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D207" t="s">
-        <v>404</v>
+        <v>11</v>
       </c>
       <c r="E207" t="s">
-        <v>405</v>
+        <v>22</v>
       </c>
       <c r="F207" t="s">
-        <v>406</v>
+        <v>23</v>
       </c>
       <c r="G207" t="s">
-        <v>407</v>
+        <v>24</v>
       </c>
       <c r="H207" t="s">
-        <v>408</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B208" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C208" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D208" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E208" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="F208" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="G208" t="s">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="H208" t="s">
-        <v>20</v>
+        <v>431</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="B209" t="s">
         <v>9</v>
       </c>
       <c r="C209" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D209" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F209" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="G209" t="s">
-        <v>411</v>
+        <v>24</v>
       </c>
       <c r="H209" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B210" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D210" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F210" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G210" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H210" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="B211" t="s">
         <v>9</v>
@@ -7104,42 +7164,42 @@
         <v>10</v>
       </c>
       <c r="D211" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E211" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F211" t="s">
-        <v>23</v>
+        <v>436</v>
       </c>
       <c r="G211" t="s">
-        <v>24</v>
+        <v>437</v>
       </c>
       <c r="H211" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="B212" t="s">
         <v>9</v>
       </c>
       <c r="C212" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D212" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E212" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F212" t="s">
-        <v>416</v>
+        <v>20</v>
       </c>
       <c r="G212" t="s">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="H212" t="s">
         <v>20</v>
@@ -7147,25 +7207,25 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="B213" t="s">
         <v>9</v>
       </c>
       <c r="C213" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D213" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E213" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F213" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G213" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H213" t="s">
         <v>20</v>
@@ -7173,33 +7233,33 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="B214" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C214" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D214" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E214" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F214" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G214" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H214" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="B215" t="s">
         <v>9</v>
@@ -7220,30 +7280,30 @@
         <v>24</v>
       </c>
       <c r="H215" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="B216" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C216" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D216" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E216" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="F216" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="G216" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="H216" t="s">
         <v>20</v>
@@ -7251,184 +7311,158 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B217" t="s">
         <v>9</v>
       </c>
       <c r="C217" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D217" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E217" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F217" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="G217" t="s">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="H217" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
+        <v>444</v>
+      </c>
+      <c r="B218" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218" t="s">
+        <v>33</v>
+      </c>
+      <c r="D218" t="s">
         <v>423</v>
       </c>
-      <c r="B218" t="s">
-        <v>9</v>
-      </c>
-      <c r="C218" t="s">
-        <v>10</v>
-      </c>
-      <c r="D218" t="s">
-        <v>11</v>
-      </c>
       <c r="E218" t="s">
-        <v>22</v>
+        <v>424</v>
       </c>
       <c r="F218" t="s">
-        <v>23</v>
+        <v>425</v>
       </c>
       <c r="G218" t="s">
-        <v>24</v>
+        <v>426</v>
       </c>
       <c r="H218" t="s">
-        <v>70</v>
+        <v>445</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="B219" t="s">
         <v>9</v>
       </c>
       <c r="C219" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D219" t="s">
-        <v>404</v>
+        <v>27</v>
       </c>
       <c r="E219" t="s">
-        <v>405</v>
+        <v>99</v>
       </c>
       <c r="F219" t="s">
-        <v>406</v>
+        <v>100</v>
       </c>
       <c r="G219" t="s">
-        <v>407</v>
+        <v>101</v>
       </c>
       <c r="H219" t="s">
-        <v>425</v>
+        <v>223</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
+        <v>447</v>
+      </c>
+      <c r="B220" t="s">
+        <v>9</v>
+      </c>
+      <c r="C220" t="s">
+        <v>33</v>
+      </c>
+      <c r="D220" t="s">
+        <v>423</v>
+      </c>
+      <c r="E220" t="s">
+        <v>424</v>
+      </c>
+      <c r="F220" t="s">
+        <v>425</v>
+      </c>
+      <c r="G220" t="s">
         <v>426</v>
       </c>
-      <c r="B220" t="s">
-        <v>9</v>
-      </c>
-      <c r="C220" t="s">
-        <v>10</v>
-      </c>
-      <c r="D220" t="s">
-        <v>27</v>
-      </c>
-      <c r="E220" t="s">
-        <v>98</v>
-      </c>
-      <c r="F220" t="s">
-        <v>99</v>
-      </c>
-      <c r="G220" t="s">
-        <v>100</v>
-      </c>
       <c r="H220" t="s">
-        <v>216</v>
+        <v>445</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="B221" t="s">
         <v>9</v>
       </c>
       <c r="C221" t="s">
-        <v>33</v>
+        <v>290</v>
       </c>
       <c r="D221" t="s">
-        <v>404</v>
+        <v>291</v>
       </c>
       <c r="E221" t="s">
-        <v>405</v>
+        <v>292</v>
       </c>
       <c r="F221" t="s">
-        <v>406</v>
+        <v>293</v>
       </c>
       <c r="G221" t="s">
-        <v>407</v>
+        <v>294</v>
       </c>
       <c r="H221" t="s">
-        <v>425</v>
+        <v>20</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B222" t="s">
         <v>9</v>
       </c>
       <c r="C222" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D222" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E222" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F222" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G222" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H222" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>429</v>
-      </c>
-      <c r="B223" t="s">
-        <v>9</v>
-      </c>
-      <c r="C223" t="s">
-        <v>280</v>
-      </c>
-      <c r="D223" t="s">
-        <v>281</v>
-      </c>
-      <c r="E223" t="s">
-        <v>282</v>
-      </c>
-      <c r="F223" t="s">
-        <v>283</v>
-      </c>
-      <c r="G223" t="s">
-        <v>284</v>
-      </c>
-      <c r="H223" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
